--- a/scripts/templates/career-sheet.xlsx
+++ b/scripts/templates/career-sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10404"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B7B441-A080-B44E-8E0C-5AD375633E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D523C20-E49A-5747-A7A9-16D4A584914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,14 +92,6 @@
     <t>自己PR</t>
   </si>
   <si>
-    <t>＜自己PR＞
-{{selfPR.summary}}
-＜経歴＞
-{{selfPR.careerHistory|join:"\n"}}
-プロジェクト一覧について：
-{{projectsDisclaimer}}</t>
-  </si>
-  <si>
     <t>期間</t>
   </si>
   <si>
@@ -228,6 +220,16 @@
   </si>
   <si>
     <t>{{/each}}</t>
+  </si>
+  <si>
+    <t>＜自己PR＞
+{{selfPR.summary}}
+＜経歴＞
+{{selfPR.careerHistory|join:"\n"}}
+Github: ogata-ryosuke
+プロジェクト一覧について：
+{{projectsDisclaimer}}</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -380,22 +382,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -749,275 +751,275 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="53.25" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
     </row>
     <row r="2" spans="1:15" ht="46.75" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
+      <c r="B2" s="11"/>
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
     </row>
     <row r="3" spans="1:15" ht="46.75" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12"/>
+      <c r="B3" s="11"/>
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
     </row>
     <row r="4" spans="1:15" ht="70.75" customHeight="1">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:15" ht="46.75" customHeight="1">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:15" ht="118.75" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
     </row>
     <row r="7" spans="1:15" ht="83" customHeight="1">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
     </row>
     <row r="8" spans="1:15" ht="87" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
     </row>
     <row r="9" spans="1:15" ht="306" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+    </row>
+    <row r="11" spans="1:15" ht="40" customHeight="1">
+      <c r="A11" s="15"/>
+      <c r="B11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-    </row>
-    <row r="11" spans="1:15" ht="40" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="1:15" ht="120" customHeight="1">
+      <c r="A12" s="15"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-    </row>
-    <row r="12" spans="1:15" ht="120" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="M12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="N12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="O12" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="17" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1035,95 +1037,78 @@
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" ht="33.25" customHeight="1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+    </row>
+    <row r="15" spans="1:15" ht="323" customHeight="1">
+      <c r="A15" s="14"/>
+      <c r="B15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" ht="323" customHeight="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="K15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="M15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E2:O2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:O3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="E4:O4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:O5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:O7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:O8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:O9"/>
     <mergeCell ref="B14:O14"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="I11:O11"/>
@@ -1135,6 +1120,23 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:O7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:O8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:O9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E4:O4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:O5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:O6"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="E2:O2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:O3"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
